--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484741_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484741_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.0631</v>
+        <v>11.7174</v>
       </c>
       <c r="E2" t="n">
-        <v>10.0705</v>
+        <v>10.4603</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9926</v>
+        <v>1.2571</v>
       </c>
       <c r="G2" t="n">
         <v>9.120100000000001</v>
@@ -610,13 +610,13 @@
         <v>3.5853</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7178</v>
+        <v>-0.0635</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5262</v>
+        <v>-0.1365</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1916</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>0.019</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7592</v>
+        <v>2.6081</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7577</v>
+        <v>1.686</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0015</v>
+        <v>0.9221</v>
       </c>
       <c r="G3" t="n">
         <v>0.4172</v>
@@ -688,13 +688,13 @@
         <v>3.5853</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2855</v>
+        <v>1.1344</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6018</v>
+        <v>0.53</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6838</v>
+        <v>0.6044</v>
       </c>
       <c r="V3" t="n">
         <v>1.2452</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6956</v>
+        <v>2.2543</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2647</v>
+        <v>0.1672</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4309</v>
+        <v>2.087</v>
       </c>
       <c r="G4" t="n">
         <v>0.4209</v>
@@ -766,13 +766,13 @@
         <v>3.2079</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2557</v>
+        <v>0.8143</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3585</v>
+        <v>0.2611</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8971</v>
+        <v>0.5532</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3018</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. GONZALEZ LÓPEZ</t>
+          <t>V. VICENT TORTOSA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6339</v>
+        <v>0.6456</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6339</v>
+        <v>-0.4992</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1.1448</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6339</v>
+        <v>-0.6057</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6339</v>
+        <v>-1.7875</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1.1817</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6339</v>
+        <v>0.3758</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6339</v>
+        <v>-0.8922</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.268</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-0.9815</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.8953</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.0863</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.6983</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.2328</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.428</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.2072</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2072</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V. VICENT TORTOSA</t>
+          <t>J. GONZALEZ LÓPEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4881</v>
+        <v>0.6339</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9477</v>
+        <v>0.6339</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4358</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6057</v>
+        <v>0.6339</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.7875</v>
+        <v>0.6339</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1817</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3758</v>
+        <v>0.6339</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.8922</v>
+        <v>0.6339</v>
       </c>
       <c r="L6" t="n">
-        <v>1.268</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9815</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8953</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0863</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1887</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6983</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.07530000000000001</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6438</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.719</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2072</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2072</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0234</v>
+        <v>0.4828</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0892</v>
+        <v>0.2841</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0658</v>
+        <v>0.1988</v>
       </c>
       <c r="G7" t="n">
         <v>-1.9297</v>
@@ -1000,13 +1000,13 @@
         <v>3.0192</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1793</v>
+        <v>0.6387</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1822</v>
+        <v>0.377</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0029</v>
+        <v>0.2616</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3018</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0651</v>
+        <v>-0.7682</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.471</v>
+        <v>-0.4122</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5941</v>
+        <v>-0.356</v>
       </c>
       <c r="G8" t="n">
         <v>1.2632</v>
@@ -1078,13 +1078,13 @@
         <v>1.3209</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8189</v>
+        <v>-0.522</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5879</v>
+        <v>-0.5291</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.231</v>
+        <v>0.0071</v>
       </c>
       <c r="V8" t="n">
         <v>-1.8868</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.584</v>
+        <v>-1.3748</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4983</v>
+        <v>-1.342</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0857</v>
+        <v>-0.0328</v>
       </c>
       <c r="G9" t="n">
         <v>-0.9479</v>
@@ -1156,13 +1156,13 @@
         <v>0.7548</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4474</v>
+        <v>-0.2382</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.4904</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1993</v>
+        <v>0.2522</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. GARCIA RUIZ</t>
+          <t>M. LOPEZ RICO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7767</v>
+        <v>-1.8192</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0088</v>
+        <v>-0.9435</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2321</v>
+        <v>-0.8757</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1499</v>
+        <v>-1.7163</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7364000000000001</v>
+        <v>-1.2835</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4135</v>
+        <v>-0.4329</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7743</v>
+        <v>-0.6496</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2481</v>
+        <v>-0.6496</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5262</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3756</v>
+        <v>-1.0668</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4883</v>
+        <v>-0.6339</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8873</v>
+        <v>-0.4329</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5661</v>
+        <v>0.1887</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5096</v>
+        <v>0.1887</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4297</v>
+        <v>-0.2916</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.291</v>
+        <v>-0.2939</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7208</v>
+        <v>0.0024</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6226</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6226</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. LOPEZ RICO</t>
+          <t>A. GARCIA RUIZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8986</v>
+        <v>-2.3541</v>
       </c>
       <c r="E11" t="n">
+        <v>-2.2423</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.1118</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-2.1499</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.7364000000000001</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-1.4135</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0.7743</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.2481</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.5262</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-1.3756</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.4883</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.8873</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.5661</v>
+      </c>
+      <c r="Q11" t="n">
         <v>-0.9435</v>
       </c>
-      <c r="F11" t="n">
-        <v>-0.9550999999999999</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-1.7163</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-1.2835</v>
-      </c>
-      <c r="I11" t="n">
-        <v>-0.4329</v>
-      </c>
-      <c r="J11" t="n">
-        <v>-0.6496</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-0.6496</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>-1.0668</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-0.6339</v>
-      </c>
-      <c r="O11" t="n">
-        <v>-0.4329</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.1887</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
-        <v>0.1887</v>
+        <v>1.5096</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3709</v>
+        <v>-0.1477</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2939</v>
+        <v>-0.5246</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.077</v>
+        <v>0.3769</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.6226</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5919</v>
+        <v>-2.5029</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.0309</v>
+        <v>-3.836</v>
       </c>
       <c r="F12" t="n">
-        <v>1.439</v>
+        <v>1.3331</v>
       </c>
       <c r="G12" t="n">
         <v>-0.7563</v>
@@ -1390,13 +1390,13 @@
         <v>1.3209</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0241</v>
+        <v>0.065</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4703</v>
+        <v>-0.2754</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4462</v>
+        <v>0.3404</v>
       </c>
       <c r="V12" t="n">
         <v>0.6415999999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.9412</v>
+        <v>-3.423</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.0414</v>
+        <v>-2.7877</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8998</v>
+        <v>-0.6353</v>
       </c>
       <c r="G13" t="n">
         <v>-5.0807</v>
@@ -1468,13 +1468,13 @@
         <v>2.4531</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0682</v>
+        <v>0.45</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1234</v>
+        <v>0.377</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1916</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3018</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.805800000000003</v>
+        <v>6.0999</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8744000000000001</v>
+        <v>1.168599999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>4.9314</v>
+        <v>4.9313</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.331200000000001</v>
+        <v>-1.331199999999999</v>
       </c>
       <c r="H14" t="n">
         <v>-8.366</v>
@@ -1522,10 +1522,10 @@
         <v>13.2222</v>
       </c>
       <c r="K14" t="n">
-        <v>5.540600000000002</v>
+        <v>5.5406</v>
       </c>
       <c r="L14" t="n">
-        <v>7.681700000000002</v>
+        <v>7.6817</v>
       </c>
       <c r="M14" t="n">
         <v>-14.5536</v>
@@ -1546,19 +1546,19 @@
         <v>22.644</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7782</v>
+        <v>2.0722</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1939</v>
+        <v>-0.9000000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>2.9721</v>
+        <v>2.972</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3018000000000002</v>
       </c>
       <c r="W14" t="n">
-        <v>5.829199999999999</v>
+        <v>5.8292</v>
       </c>
       <c r="X14" t="n">
         <v>-6.131000000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0291</v>
+        <v>3.0728</v>
       </c>
       <c r="E15" t="n">
-        <v>4.9339</v>
+        <v>4.057</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9048</v>
+        <v>-0.9842</v>
       </c>
       <c r="G15" t="n">
         <v>4.8909</v>
@@ -1624,13 +1624,13 @@
         <v>2.2644</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9494</v>
+        <v>-0.0069</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7388</v>
+        <v>-0.1381</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2106</v>
+        <v>0.1312</v>
       </c>
       <c r="V15" t="n">
         <v>-2.1886</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. BLAZQUEZ GONZALEZ</t>
+          <t>T. GOODMAN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.7537</v>
+        <v>2.9757</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5282</v>
+        <v>3.0155</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2255</v>
+        <v>-0.0398</v>
       </c>
       <c r="G16" t="n">
-        <v>2.3443</v>
+        <v>6.3183</v>
       </c>
       <c r="H16" t="n">
-        <v>3.0435</v>
+        <v>5.9195</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6992</v>
+        <v>0.3988</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8193</v>
+        <v>7.192</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3454</v>
+        <v>6.3609</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5262</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>0.525</v>
+        <v>-0.8737</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6981000000000001</v>
+        <v>-0.4413</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.173</v>
+        <v>-0.4323</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1887</v>
+        <v>-3.9627</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9435</v>
+        <v>-6.6045</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1322</v>
+        <v>2.6418</v>
       </c>
       <c r="S16" t="n">
-        <v>1.5225</v>
+        <v>-0.6062</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6525</v>
+        <v>-0.3453</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8701</v>
+        <v>-0.2609</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3018</v>
+        <v>1.2262</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.7732</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3018</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. GOODMAN</t>
+          <t>P. BLAZQUEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5079</v>
+        <v>2.9659</v>
       </c>
       <c r="E17" t="n">
-        <v>2.918</v>
+        <v>0.8462</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4102</v>
+        <v>2.1197</v>
       </c>
       <c r="G17" t="n">
-        <v>6.3183</v>
+        <v>2.3443</v>
       </c>
       <c r="H17" t="n">
-        <v>5.9195</v>
+        <v>3.0435</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3988</v>
+        <v>-0.6992</v>
       </c>
       <c r="J17" t="n">
-        <v>7.192</v>
+        <v>1.8193</v>
       </c>
       <c r="K17" t="n">
-        <v>6.3609</v>
+        <v>2.3454</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8310999999999999</v>
+        <v>-0.5262</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8737</v>
+        <v>0.525</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4413</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4323</v>
+        <v>-0.173</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.9627</v>
+        <v>0.1887</v>
       </c>
       <c r="Q17" t="n">
-        <v>-6.6045</v>
+        <v>-0.9435</v>
       </c>
       <c r="R17" t="n">
-        <v>2.6418</v>
+        <v>1.1322</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.074</v>
+        <v>0.7347</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4427</v>
+        <v>-0.0296</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6313</v>
+        <v>0.7642</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2262</v>
+        <v>-0.3018</v>
       </c>
       <c r="W17" t="n">
-        <v>2.7732</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.547</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="18">
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. SARRIAS SANCHEZ</t>
+          <t>H. RODRÍGUEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4401</v>
+        <v>0.317</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6658</v>
+        <v>0.317</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2257</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8159999999999999</v>
+        <v>0.317</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1387</v>
+        <v>0.317</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.9547</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2.2721</v>
+        <v>0.317</v>
       </c>
       <c r="K19" t="n">
-        <v>2.8635</v>
+        <v>0.317</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5914</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.0881</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.7248</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3633</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3774</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2644</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6684</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2664</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.402</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.547</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.547</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>H. RODRÍGUEZ GUTIERREZ</t>
+          <t>D. SARRIAS SANCHEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.317</v>
+        <v>0.2633</v>
       </c>
       <c r="E20" t="n">
-        <v>0.317</v>
+        <v>1.5683</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>-1.3051</v>
       </c>
       <c r="G20" t="n">
-        <v>0.317</v>
+        <v>-0.8159999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>0.317</v>
+        <v>1.1387</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>-1.9547</v>
       </c>
       <c r="J20" t="n">
-        <v>0.317</v>
+        <v>2.2721</v>
       </c>
       <c r="K20" t="n">
-        <v>0.317</v>
+        <v>2.8635</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0.5914</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>-3.0881</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>-1.7248</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-1.3633</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.3774</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.2644</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-0.8452</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>-0.3638</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>-0.4814</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.547</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.547</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. PAREDES PEREZ</t>
+          <t>E. RHAIEM SANCHEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1225</v>
+        <v>-0.0327</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0588</v>
+        <v>-0.577</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0638</v>
+        <v>0.5443</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0814</v>
+        <v>-0.9482</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0814</v>
+        <v>-1.0134</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.1902</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>0.1902</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0814</v>
+        <v>-1.1384</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0814</v>
+        <v>-1.2036</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.1322</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0412</v>
+        <v>-0.2165</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0588</v>
+        <v>-0.1254</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0176</v>
+        <v>-0.0911</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.8868</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. RHAIEM SANCHEZ</t>
+          <t>I. PAREDES PEREZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2889</v>
+        <v>-0.0961</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6744</v>
+        <v>-0.0588</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3856</v>
+        <v>-0.0373</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9482</v>
+        <v>-0.0814</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.0134</v>
+        <v>-0.0814</v>
       </c>
       <c r="I22" t="n">
-        <v>0.06519999999999999</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1902</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1902</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1384</v>
+        <v>-0.0814</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2036</v>
+        <v>-0.0814</v>
       </c>
       <c r="O22" t="n">
-        <v>0.06519999999999999</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.7548</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1322</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4726</v>
+        <v>-0.0147</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2228</v>
+        <v>-0.0588</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2498</v>
+        <v>0.0441</v>
       </c>
       <c r="V22" t="n">
-        <v>1.8868</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.6415999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4825</v>
+        <v>-0.2961</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3182</v>
+        <v>-1.0259</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8357</v>
+        <v>0.7299</v>
       </c>
       <c r="G23" t="n">
         <v>-0.2495</v>
@@ -2248,13 +2248,13 @@
         <v>1.3209</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3086</v>
+        <v>-0.1221</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7984</v>
+        <v>-0.506</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4898</v>
+        <v>0.3839</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3018</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.1157</v>
+        <v>-1.9918</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.9412</v>
+        <v>-1.8437</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1745</v>
+        <v>-0.148</v>
       </c>
       <c r="G24" t="n">
         <v>-1.8858</v>
@@ -2326,13 +2326,13 @@
         <v>0.7548</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0412</v>
+        <v>0.0827</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4115</v>
+        <v>-0.3141</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3704</v>
+        <v>0.3968</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.8336</v>
+        <v>-5.6374</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.2069</v>
+        <v>-4.7197</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6267</v>
+        <v>-0.9177</v>
       </c>
       <c r="G25" t="n">
         <v>-4.7228</v>
@@ -2404,13 +2404,13 @@
         <v>2.8305</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4691</v>
+        <v>-0.2729</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.1634</v>
+        <v>-0.6762</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6944</v>
+        <v>0.4034</v>
       </c>
       <c r="V25" t="n">
         <v>0.3018</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-9.2783</v>
+        <v>-8.6144</v>
       </c>
       <c r="E26" t="n">
-        <v>-8.3626</v>
+        <v>-7.778</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.9157</v>
+        <v>-0.8364</v>
       </c>
       <c r="G26" t="n">
         <v>-5.1032</v>
@@ -2482,13 +2482,13 @@
         <v>2.6418</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.1751</v>
+        <v>-0.5111</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.9994</v>
+        <v>-0.4148</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1757</v>
+        <v>-0.0963</v>
       </c>
       <c r="V26" t="n">
         <v>-1.8678</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.8059</v>
+        <v>-5.806</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.931400000000001</v>
+        <v>-4.931300000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.8746000000000003</v>
+        <v>-0.8746000000000002</v>
       </c>
       <c r="G27" t="n">
         <v>1.3314</v>
@@ -2530,7 +2530,7 @@
         <v>8.366000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>-7.034699999999999</v>
+        <v>-7.0347</v>
       </c>
       <c r="J27" t="n">
         <v>14.5535</v>
@@ -2560,13 +2560,13 @@
         <v>16.983</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.7783</v>
+        <v>-1.7782</v>
       </c>
       <c r="T27" t="n">
         <v>-2.9721</v>
       </c>
       <c r="U27" t="n">
-        <v>1.1941</v>
+        <v>1.1939</v>
       </c>
       <c r="V27" t="n">
         <v>0.3017999999999996</v>
